--- a/artfynd/A 53309-2023 artfynd.xlsx
+++ b/artfynd/A 53309-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126052947</v>
       </c>
       <c r="B2" t="n">
-        <v>58326</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126052923</v>
       </c>
       <c r="B3" t="n">
-        <v>57597</v>
+        <v>57598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126052914</v>
       </c>
       <c r="B4" t="n">
-        <v>57524</v>
+        <v>57525</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53309-2023 artfynd.xlsx
+++ b/artfynd/A 53309-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126052947</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126052923</v>
       </c>
       <c r="B3" t="n">
-        <v>57598</v>
+        <v>57602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126052914</v>
       </c>
       <c r="B4" t="n">
-        <v>57525</v>
+        <v>57529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53309-2023 artfynd.xlsx
+++ b/artfynd/A 53309-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126052947</v>
       </c>
       <c r="B2" t="n">
-        <v>58331</v>
+        <v>58334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>126052923</v>
       </c>
       <c r="B3" t="n">
-        <v>57602</v>
+        <v>57603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126052914</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57530</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 53309-2023 artfynd.xlsx
+++ b/artfynd/A 53309-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126052947</v>
+        <v>126052923</v>
       </c>
       <c r="B2" t="n">
-        <v>58334</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -703,14 +703,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -780,27 +780,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126052923</v>
+        <v>126052914</v>
       </c>
       <c r="B3" t="n">
-        <v>57603</v>
+        <v>57825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100067</v>
+        <v>100096</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -885,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126052914</v>
+        <v>126052947</v>
       </c>
       <c r="B4" t="n">
-        <v>57530</v>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100096</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fiskgjuse</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pandion haliaetus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,14 +913,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 53309-2023 artfynd.xlsx
+++ b/artfynd/A 53309-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126052923</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126052914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126052947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>